--- a/inventory/inventory_default.xlsx
+++ b/inventory/inventory_default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\meowmeow_sandbox\inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAA5635-F45A-4129-AD08-DF8C180596FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85BA35A-0A7F-4DE9-9B07-92E3863F5549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{2757FED6-37E3-4677-8046-0F44B021E7C6}"/>
   </bookViews>
@@ -215,7 +215,7 @@
     <t>Global Inveontory (Unit)</t>
   </si>
   <si>
-    <t>online (unit)</t>
+    <t>Online Inventory</t>
   </si>
 </sst>
 </file>
@@ -315,7 +315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -371,8 +371,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1240,298 +1248,362 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{377E2FFF-668E-4CF2-BB70-CEBAC8A30B23}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="24" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="25">
         <v>13</v>
       </c>
+      <c r="E2" s="25">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="25">
         <v>24</v>
       </c>
+      <c r="E3" s="25">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="25">
         <v>16</v>
       </c>
+      <c r="E4" s="25">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="25">
         <v>59</v>
       </c>
+      <c r="E5" s="25">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="25">
         <v>32</v>
       </c>
+      <c r="E6" s="25">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="25">
         <v>22</v>
       </c>
+      <c r="E7" s="25">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="25">
         <v>79</v>
       </c>
+      <c r="E8" s="25">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="25">
         <v>10</v>
       </c>
+      <c r="E9" s="25">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="21">
-        <v>6</v>
+      <c r="D10" s="25">
+        <v>1</v>
+      </c>
+      <c r="E10" s="25">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="A11" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="25">
         <v>28</v>
       </c>
+      <c r="E11" s="25">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="7" t="s">
+      <c r="A12" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="21">
-        <v>23</v>
+      <c r="D12" s="25">
+        <v>53</v>
+      </c>
+      <c r="E12" s="25">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="A13" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="25">
         <v>15</v>
       </c>
+      <c r="E13" s="25">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="A14" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="25">
         <v>50</v>
       </c>
+      <c r="E14" s="25">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="21">
-        <v>25</v>
+      <c r="D15" s="25">
+        <v>100</v>
+      </c>
+      <c r="E15" s="25">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="E16" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="E17" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="E18" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="25">
         <v>33</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="E19" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="25">
         <v>32</v>
       </c>
+      <c r="E20" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
